--- a/BOM/Use.xlsx
+++ b/BOM/Use.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF2695CE-EDF5-4694-9E90-993E2E5905E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EE276E-D2F9-49A0-AEF2-660A927F5E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{50E5FA24-8F04-4F2F-94DC-6D079599AFC2}"/>
   </bookViews>
@@ -370,10 +370,10 @@
   <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="171" formatCode="0.000"/>
-    <numFmt numFmtId="172" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="00000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -547,10 +547,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -562,10 +562,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -574,7 +574,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -592,7 +592,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -634,13 +634,22 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -655,16 +664,7 @@
     <xf numFmtId="1" fontId="4" fillId="2" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="2" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -988,6 +988,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374468E5-9CA0-4A55-A31A-BC7E7728083D}">
   <dimension ref="A1:AK39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="19" max="19" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="59.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
@@ -996,10 +1004,10 @@
       <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="43" t="s">
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="33" t="s">
@@ -1034,70 +1042,70 @@
       <c r="T1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="36" t="s">
+      <c r="U1" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="V1" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="38" t="s">
+      <c r="W1" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="39" t="s">
+      <c r="X1" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="40" t="s">
+      <c r="Y1" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="40" t="s">
+      <c r="Z1" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB1" s="38" t="s">
+      <c r="AA1" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB1" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="41" t="s">
+      <c r="AC1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="41" t="s">
+      <c r="AD1" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="34" t="s">
+      <c r="AE1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="34" t="s">
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="AI1" s="34"/>
-      <c r="AJ1" s="35" t="s">
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="AK1" s="35" t="s">
+      <c r="AK1" s="38" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="33"/>
       <c r="B2" s="33"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
       <c r="E2" s="33"/>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
+      <c r="G2" s="34"/>
+      <c r="H2" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42" t="s">
+      <c r="I2" s="34"/>
+      <c r="J2" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="42"/>
+      <c r="K2" s="34"/>
       <c r="L2" s="30"/>
       <c r="M2" s="31" t="s">
         <v>25</v>
@@ -1113,23 +1121,23 @@
       <c r="R2" s="33"/>
       <c r="S2" s="33"/>
       <c r="T2" s="33"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
     </row>
     <row r="3" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4774,20 +4782,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
     <mergeCell ref="T1:T2"/>
     <mergeCell ref="AI1:AI2"/>
     <mergeCell ref="AJ1:AJ2"/>
@@ -4804,6 +4798,20 @@
     <mergeCell ref="AD1:AD2"/>
     <mergeCell ref="AE1:AG2"/>
     <mergeCell ref="AH1:AH2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/BOM/Use.xlsx
+++ b/BOM/Use.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9295F5-5597-4309-9C82-711C983F3E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A287FB8-347A-4303-BC8F-717E110EE736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{50E5FA24-8F04-4F2F-94DC-6D079599AFC2}"/>
+    <workbookView xWindow="-20775" yWindow="3240" windowWidth="14400" windowHeight="7275" xr2:uid="{50E5FA24-8F04-4F2F-94DC-6D079599AFC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="104">
   <si>
     <t>No.</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>LLL</t>
+  </si>
+  <si>
+    <t>P Sloc</t>
   </si>
 </sst>
 </file>
@@ -600,6 +603,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -622,9 +628,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -974,7 +977,7 @@
     <col min="28" max="28" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="29" max="31" width="6.81640625" customWidth="1"/>
     <col min="32" max="32" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.08984375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="21.26953125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1018,49 +1021,51 @@
       <c r="R1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="36" t="s">
+      <c r="T1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="U1" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="38" t="s">
+      <c r="V1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="39" t="s">
+      <c r="W1" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="X1" s="39" t="s">
+      <c r="X1" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" s="37" t="s">
+      <c r="Y1" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" s="40" t="s">
+      <c r="AA1" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AB1" s="40" t="s">
+      <c r="AB1" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="33" t="s">
+      <c r="AC1" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33" t="s">
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="34" t="s">
+      <c r="AG1" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="AI1" s="34" t="s">
+      <c r="AI1" s="35" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1068,18 +1073,18 @@
       <c r="A2" s="32"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="41"/>
+      <c r="I2" s="33"/>
       <c r="J2" s="29"/>
       <c r="K2" s="30" t="s">
         <v>24</v>
@@ -1095,23 +1100,23 @@
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
       <c r="R2" s="32"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="34"/>
+      <c r="AD2" s="34"/>
+      <c r="AE2" s="34"/>
+      <c r="AF2" s="34"/>
+      <c r="AG2" s="34"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
     </row>
     <row r="3" spans="1:35" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4538,18 +4543,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="AH1:AH2"/>
@@ -4566,6 +4559,18 @@
     <mergeCell ref="AB1:AB2"/>
     <mergeCell ref="AC1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
